--- a/data.mn/public/datasets/sown-area-total-mongolia.xlsx
+++ b/data.mn/public/datasets/sown-area-total-mongolia.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -963,4 +964,562 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>тариалсан_талбай</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B2" t="n">
+        <v>265.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B3" t="n">
+        <v>382.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B4" t="n">
+        <v>439.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B5" t="n">
+        <v>455.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B6" t="n">
+        <v>453.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B7" t="n">
+        <v>480.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B8" t="n">
+        <v>460.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B9" t="n">
+        <v>482.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B10" t="n">
+        <v>492.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B11" t="n">
+        <v>490.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B12" t="n">
+        <v>454.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B13" t="n">
+        <v>464.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B14" t="n">
+        <v>475.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B15" t="n">
+        <v>488.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B16" t="n">
+        <v>494.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B17" t="n">
+        <v>509.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B18" t="n">
+        <v>538.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B19" t="n">
+        <v>592.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B20" t="n">
+        <v>681.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B21" t="n">
+        <v>697.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B22" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B23" t="n">
+        <v>683.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B24" t="n">
+        <v>641.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>723.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B26" t="n">
+        <v>756.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B27" t="n">
+        <v>789.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>803.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B29" t="n">
+        <v>800.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B30" t="n">
+        <v>828.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B31" t="n">
+        <v>837.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B32" t="n">
+        <v>787.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B33" t="n">
+        <v>708.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B34" t="n">
+        <v>657.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B35" t="n">
+        <v>584.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B36" t="n">
+        <v>470.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B37" t="n">
+        <v>372.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B38" t="n">
+        <v>347.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B39" t="n">
+        <v>333.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B40" t="n">
+        <v>326.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B41" t="n">
+        <v>296.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B42" t="n">
+        <v>209.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>217.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B44" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B45" t="n">
+        <v>225.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B46" t="n">
+        <v>200.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B47" t="n">
+        <v>189.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B48" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B49" t="n">
+        <v>202.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B50" t="n">
+        <v>192.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B51" t="n">
+        <v>282.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B52" t="n">
+        <v>316.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B53" t="n">
+        <v>347.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B54" t="n">
+        <v>381.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B55" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B56" t="n">
+        <v>444.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B57" t="n">
+        <v>527.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B58" t="n">
+        <v>508.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B59" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B60" t="n">
+        <v>511.8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B61" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B62" t="n">
+        <v>591.2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B63" t="n">
+        <v>678.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B64" t="n">
+        <v>621.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B65" t="n">
+        <v>645.8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B66" t="n">
+        <v>635.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B67" t="n">
+        <v>601.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>